--- a/salidas/empresas/JPM.xlsx
+++ b/salidas/empresas/JPM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>23.46864700317383</v>
+        <v>23.46864891052246</v>
       </c>
       <c r="C2" t="n">
         <v>39.75</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>24.28931427001953</v>
+        <v>24.28931999206543</v>
       </c>
       <c r="C3" t="n">
         <v>41.13999938964844</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.58451843261719</v>
+        <v>24.58450698852539</v>
       </c>
       <c r="C4" t="n">
         <v>41.63999938964844</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.01166343688965</v>
+        <v>27.01167106628418</v>
       </c>
       <c r="C5" t="n">
         <v>45.38000106811523</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>25.38072967529297</v>
+        <v>25.38073348999023</v>
       </c>
       <c r="C6" t="n">
         <v>42.63999938964844</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>24.99978637695312</v>
+        <v>24.99977111816406</v>
       </c>
       <c r="C7" t="n">
         <v>42</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>27.37613296508789</v>
+        <v>27.37613868713379</v>
       </c>
       <c r="C8" t="n">
         <v>45.61999893188477</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.18026542663574</v>
+        <v>28.18027305603027</v>
       </c>
       <c r="C10" t="n">
         <v>46.95999908447266</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>28.67246437072754</v>
+        <v>28.67246246337891</v>
       </c>
       <c r="C11" t="n">
         <v>47.43999862670898</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>27.97136497497559</v>
+        <v>27.97136688232422</v>
       </c>
       <c r="C12" t="n">
         <v>46.27999877929688</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>29.19223213195801</v>
+        <v>29.1922550201416</v>
       </c>
       <c r="C13" t="n">
         <v>48.29999923706055</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.00002479553223</v>
+        <v>31.0000171661377</v>
       </c>
       <c r="C14" t="n">
         <v>50.93000030517578</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.06266784667969</v>
+        <v>30.06265830993652</v>
       </c>
       <c r="C15" t="n">
         <v>49.38999938964844</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>29.44789123535156</v>
+        <v>29.44790077209473</v>
       </c>
       <c r="C16" t="n">
         <v>48.38000106811523</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>31.93728256225586</v>
+        <v>31.93727684020996</v>
       </c>
       <c r="C17" t="n">
         <v>52.09999847412109</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>31.77175903320312</v>
+        <v>31.77178382873535</v>
       </c>
       <c r="C18" t="n">
         <v>51.83000183105469</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>29.69982147216797</v>
+        <v>29.69980430603027</v>
       </c>
       <c r="C19" t="n">
         <v>48.45000076293945</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>27.18831253051758</v>
+        <v>27.18831062316895</v>
       </c>
       <c r="C20" t="n">
         <v>44.0099983215332</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>27.50337600708008</v>
+        <v>27.50337791442871</v>
       </c>
       <c r="C21" t="n">
         <v>44.52000045776367</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.30648803710938</v>
+        <v>28.30649757385254</v>
       </c>
       <c r="C22" t="n">
         <v>45.81999969482422</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>29.27133178710938</v>
+        <v>29.27132415771484</v>
       </c>
       <c r="C23" t="n">
         <v>47</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>28.41185188293457</v>
+        <v>28.41186141967773</v>
       </c>
       <c r="C24" t="n">
         <v>45.61999893188477</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>27.18496131896973</v>
+        <v>27.18495559692383</v>
       </c>
       <c r="C25" t="n">
         <v>43.65000152587891</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.77969360351562</v>
+        <v>29.77967643737793</v>
       </c>
       <c r="C26" t="n">
         <v>47.40000152587891</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>25.53891944885254</v>
+        <v>25.53890609741211</v>
       </c>
       <c r="C27" t="n">
         <v>40.65000152587891</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>26.98392105102539</v>
+        <v>26.98391532897949</v>
       </c>
       <c r="C28" t="n">
         <v>42.95000076293945</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>30.1807804107666</v>
+        <v>30.1807746887207</v>
       </c>
       <c r="C29" t="n">
         <v>47.65000152587891</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>27.23553276062012</v>
+        <v>27.23551750183105</v>
       </c>
       <c r="C30" t="n">
         <v>43</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.02262115478516</v>
+        <v>26.02263259887695</v>
       </c>
       <c r="C32" t="n">
         <v>40.63000106811523</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.91032218933105</v>
+        <v>29.91033172607422</v>
       </c>
       <c r="C34" t="n">
         <v>46.70000076293945</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>26.62356376647949</v>
+        <v>26.62356758117676</v>
       </c>
       <c r="C35" t="n">
         <v>41.25</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.43399620056152</v>
+        <v>20.43399047851562</v>
       </c>
       <c r="C36" t="n">
         <v>31.65999984741211</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.35008430480957</v>
+        <v>20.35009002685547</v>
       </c>
       <c r="C37" t="n">
         <v>31.53000068664551</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>16.66551208496094</v>
+        <v>16.66551399230957</v>
       </c>
       <c r="C38" t="n">
         <v>25.51000022888184</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.9277515411377</v>
+        <v>14.92775440216064</v>
       </c>
       <c r="C39" t="n">
         <v>22.85000038146973</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.5970516204834</v>
+        <v>21.59704780578613</v>
       </c>
       <c r="C41" t="n">
         <v>33</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>24.14942932128906</v>
+        <v>24.14943695068359</v>
       </c>
       <c r="C42" t="n">
         <v>36.90000152587891</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>22.32349967956543</v>
+        <v>22.3234920501709</v>
       </c>
       <c r="C43" t="n">
         <v>34.11000061035156</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.33185958862305</v>
+        <v>25.33185577392578</v>
       </c>
       <c r="C44" t="n">
         <v>38.65000152587891</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.48441505432129</v>
+        <v>28.48442459106445</v>
       </c>
       <c r="C45" t="n">
         <v>43.45999908447266</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>28.72037315368652</v>
+        <v>28.72036743164062</v>
       </c>
       <c r="C46" t="n">
         <v>43.81999969482422</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.40989685058594</v>
+        <v>27.40988349914551</v>
       </c>
       <c r="C47" t="n">
         <v>41.77000045776367</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>27.88236618041992</v>
+        <v>27.88236808776855</v>
       </c>
       <c r="C48" t="n">
         <v>42.4900016784668</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.34426689147949</v>
+        <v>27.34426307678223</v>
       </c>
       <c r="C49" t="n">
         <v>41.66999816894531</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.58351516723633</v>
+        <v>25.58352279663086</v>
       </c>
       <c r="C50" t="n">
         <v>38.93999862670898</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>27.57420539855957</v>
+        <v>27.5742130279541</v>
       </c>
       <c r="C51" t="n">
         <v>41.97000122070312</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.40067672729492</v>
+        <v>29.40067100524902</v>
       </c>
       <c r="C52" t="n">
         <v>44.75</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>28.00627708435059</v>
+        <v>28.00627899169922</v>
       </c>
       <c r="C53" t="n">
         <v>42.58000183105469</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>26.0330867767334</v>
+        <v>26.03309059143066</v>
       </c>
       <c r="C54" t="n">
         <v>39.58000183105469</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.07960891723633</v>
+        <v>24.07961082458496</v>
       </c>
       <c r="C55" t="n">
         <v>36.61000061035156</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>26.52972030639648</v>
+        <v>26.52972412109375</v>
       </c>
       <c r="C56" t="n">
         <v>40.27999877929688</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.94788360595703</v>
+        <v>23.9478931427002</v>
       </c>
       <c r="C57" t="n">
         <v>36.36000061035156</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.06757354736328</v>
+        <v>25.06755638122559</v>
       </c>
       <c r="C58" t="n">
         <v>38.06000137329102</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>24.81631278991699</v>
+        <v>24.81632232666016</v>
       </c>
       <c r="C59" t="n">
         <v>37.63000106811523</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>24.66464042663574</v>
+        <v>24.66464805603027</v>
       </c>
       <c r="C60" t="n">
         <v>37.40000152587891</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>27.97524642944336</v>
+        <v>27.97524833679199</v>
       </c>
       <c r="C61" t="n">
         <v>42.41999816894531</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>29.67117309570312</v>
+        <v>29.67116928100586</v>
       </c>
       <c r="C62" t="n">
         <v>44.93999862670898</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>30.82659530639648</v>
+        <v>30.82658958435059</v>
       </c>
       <c r="C63" t="n">
         <v>46.68999862670898</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>30.43707084655762</v>
+        <v>30.43705368041992</v>
       </c>
       <c r="C64" t="n">
         <v>46.09999847412109</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>30.29012107849121</v>
+        <v>30.29013061523438</v>
       </c>
       <c r="C65" t="n">
         <v>45.63000106811523</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>28.70358085632324</v>
+        <v>28.70360374450684</v>
       </c>
       <c r="C66" t="n">
         <v>43.2400016784668</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>27.17681312561035</v>
+        <v>27.17681121826172</v>
       </c>
       <c r="C67" t="n">
         <v>40.93999862670898</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>27.01651191711426</v>
+        <v>27.01650428771973</v>
       </c>
       <c r="C68" t="n">
         <v>40.45000076293945</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>25.08627891540527</v>
+        <v>25.08628845214844</v>
       </c>
       <c r="C69" t="n">
         <v>37.56000137329102</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>20.11711311340332</v>
+        <v>20.11711120605469</v>
       </c>
       <c r="C70" t="n">
         <v>30.1200008392334</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>23.4205322265625</v>
+        <v>23.42053413391113</v>
       </c>
       <c r="C71" t="n">
         <v>34.7599983215332</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>20.86691093444824</v>
+        <v>20.86690902709961</v>
       </c>
       <c r="C72" t="n">
         <v>30.96999931335449</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>22.40312385559082</v>
+        <v>22.40312576293945</v>
       </c>
       <c r="C73" t="n">
         <v>33.25</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>25.31284141540527</v>
+        <v>25.31283950805664</v>
       </c>
       <c r="C74" t="n">
         <v>37.29999923706055</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>26.62937545776367</v>
+        <v>26.62937927246094</v>
       </c>
       <c r="C75" t="n">
         <v>39.2400016784668</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>31.20333480834961</v>
+        <v>31.20333290100098</v>
       </c>
       <c r="C76" t="n">
         <v>45.97999954223633</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>29.3583927154541</v>
+        <v>29.35837936401367</v>
       </c>
       <c r="C77" t="n">
         <v>42.97999954223633</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.6437873840332</v>
+        <v>22.6437931060791</v>
       </c>
       <c r="C78" t="n">
         <v>33.15000152587891</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>24.40612030029297</v>
+        <v>24.4061164855957</v>
       </c>
       <c r="C79" t="n">
         <v>35.72999954223633</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.79557037353516</v>
+        <v>24.79557800292969</v>
       </c>
       <c r="C80" t="n">
         <v>36</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.58077049255371</v>
+        <v>25.58077812194824</v>
       </c>
       <c r="C81" t="n">
         <v>37.13999938964844</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>27.88125038146973</v>
+        <v>27.88124656677246</v>
       </c>
       <c r="C82" t="n">
         <v>40.47999954223633</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>28.91979026794434</v>
+        <v>28.91979217529297</v>
       </c>
       <c r="C83" t="n">
         <v>41.68000030517578</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>28.50348472595215</v>
+        <v>28.50349044799805</v>
       </c>
       <c r="C84" t="n">
         <v>41.08000183105469</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>30.50871467590332</v>
+        <v>30.50872802734375</v>
       </c>
       <c r="C85" t="n">
         <v>43.97000122070312</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>32.87004470825195</v>
+        <v>32.87004852294922</v>
       </c>
       <c r="C86" t="n">
         <v>47.04999923706055</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>34.17646408081055</v>
+        <v>34.17646026611328</v>
       </c>
       <c r="C87" t="n">
         <v>48.91999816894531</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>33.15646743774414</v>
+        <v>33.15648651123047</v>
       </c>
       <c r="C88" t="n">
         <v>47.45999908447266</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>34.45341873168945</v>
+        <v>34.45342636108398</v>
       </c>
       <c r="C89" t="n">
         <v>49.0099983215332</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>38.37609481811523</v>
+        <v>38.3760871887207</v>
       </c>
       <c r="C90" t="n">
         <v>54.59000015258789</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>37.11072540283203</v>
+        <v>37.11071395874023</v>
       </c>
       <c r="C91" t="n">
         <v>52.79000091552734</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>39.46320343017578</v>
+        <v>39.46319580078125</v>
       </c>
       <c r="C92" t="n">
         <v>55.72999954223633</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>35.7809944152832</v>
+        <v>35.78099822998047</v>
       </c>
       <c r="C93" t="n">
         <v>50.52999877929688</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.60242080688477</v>
+        <v>36.60239791870117</v>
       </c>
       <c r="C94" t="n">
         <v>51.68999862670898</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>36.76507949829102</v>
+        <v>36.76506805419922</v>
       </c>
       <c r="C95" t="n">
         <v>51.54000091552734</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>40.81679916381836</v>
+        <v>40.81680297851562</v>
       </c>
       <c r="C96" t="n">
         <v>57.22000122070312</v>
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>39.74828338623047</v>
+        <v>39.7482795715332</v>
       </c>
       <c r="C98" t="n">
         <v>55.36000061035156</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>40.79656219482422</v>
+        <v>40.79655838012695</v>
       </c>
       <c r="C99" t="n">
         <v>56.81999969482422</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>43.58955764770508</v>
+        <v>43.58956527709961</v>
       </c>
       <c r="C100" t="n">
         <v>60.70999908447266</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>40.44676971435547</v>
+        <v>40.44677734375</v>
       </c>
       <c r="C101" t="n">
         <v>55.97999954223633</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>40.15053558349609</v>
+        <v>40.1505241394043</v>
       </c>
       <c r="C102" t="n">
         <v>55.56999969482422</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>41.63170623779297</v>
+        <v>41.63169860839844</v>
       </c>
       <c r="C103" t="n">
         <v>57.61999893188477</v>
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2967,7 +2979,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>44.3000602722168</v>
+        <v>44.30005645751953</v>
       </c>
       <c r="C107" t="n">
         <v>60.47999954223633</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>44.06567001342773</v>
+        <v>44.06566619873047</v>
       </c>
       <c r="C108" t="n">
         <v>60.15999984741211</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>45.83825302124023</v>
+        <v>45.8382453918457</v>
       </c>
       <c r="C109" t="n">
         <v>62.58000183105469</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>40.08820343017578</v>
+        <v>40.08819961547852</v>
       </c>
       <c r="C110" t="n">
         <v>54.38000106811523</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>45.17480087280273</v>
+        <v>45.17480850219727</v>
       </c>
       <c r="C111" t="n">
         <v>61.27999877929688</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>44.65875625610352</v>
+        <v>44.65876007080078</v>
       </c>
       <c r="C112" t="n">
         <v>60.58000183105469</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>46.94438934326172</v>
+        <v>46.94438552856445</v>
       </c>
       <c r="C113" t="n">
         <v>63.2599983215332</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>48.81443786621094</v>
+        <v>48.8144416809082</v>
       </c>
       <c r="C114" t="n">
         <v>65.77999877929688</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>50.28379058837891</v>
+        <v>50.28377151489258</v>
       </c>
       <c r="C115" t="n">
         <v>67.76000213623047</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>51.18756866455078</v>
+        <v>51.18756103515625</v>
       </c>
       <c r="C116" t="n">
         <v>68.52999877929688</v>
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>45.54073715209961</v>
+        <v>45.54071807861328</v>
       </c>
       <c r="C118" t="n">
         <v>60.97000122070312</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>48.33696746826172</v>
+        <v>48.33695220947266</v>
       </c>
       <c r="C119" t="n">
         <v>64.25</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>50.16511154174805</v>
+        <v>50.16511535644531</v>
       </c>
       <c r="C120" t="n">
         <v>66.68000030517578</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.67607879638672</v>
+        <v>49.67609786987305</v>
       </c>
       <c r="C121" t="n">
         <v>66.02999877929688</v>
@@ -3460,7 +3472,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3489,7 +3501,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>44.85162353515625</v>
+        <v>44.85163497924805</v>
       </c>
       <c r="C124" t="n">
         <v>59.22000122070312</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>48.22035980224609</v>
+        <v>48.2203483581543</v>
       </c>
       <c r="C125" t="n">
         <v>63.20000076293945</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.79972457885742</v>
+        <v>49.79972076416016</v>
       </c>
       <c r="C126" t="n">
         <v>65.26999664306641</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>47.41160202026367</v>
+        <v>47.41159820556641</v>
       </c>
       <c r="C127" t="n">
         <v>62.13999938964844</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>49.18781280517578</v>
+        <v>49.18780136108398</v>
       </c>
       <c r="C128" t="n">
         <v>63.97000122070312</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>51.90206909179688</v>
+        <v>51.902099609375</v>
       </c>
       <c r="C129" t="n">
         <v>67.5</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>51.20235824584961</v>
+        <v>51.20237350463867</v>
       </c>
       <c r="C130" t="n">
         <v>66.58999633789062</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>53.64252853393555</v>
+        <v>53.64252471923828</v>
       </c>
       <c r="C131" t="n">
         <v>69.26000213623047</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>62.09241485595703</v>
+        <v>62.0924186706543</v>
       </c>
       <c r="C132" t="n">
         <v>80.16999816894531</v>
@@ -3779,7 +3791,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>65.90940856933594</v>
+        <v>65.90941619873047</v>
       </c>
       <c r="C134" t="n">
         <v>84.62999725341797</v>
@@ -3837,7 +3849,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,7 +3907,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3924,7 +3936,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.59086608886719</v>
+        <v>71.59085083007812</v>
       </c>
       <c r="C139" t="n">
         <v>91.40000152587891</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>72.29966735839844</v>
+        <v>72.29969024658203</v>
       </c>
       <c r="C140" t="n">
         <v>91.80000305175781</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>71.58297729492188</v>
+        <v>71.58296203613281</v>
       </c>
       <c r="C141" t="n">
         <v>90.88999938964844</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>75.22158050537109</v>
+        <v>75.22156524658203</v>
       </c>
       <c r="C142" t="n">
         <v>95.51000213623047</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>79.701416015625</v>
+        <v>79.70140075683594</v>
       </c>
       <c r="C143" t="n">
         <v>100.6100006103516</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>82.79885101318359</v>
+        <v>82.79883575439453</v>
       </c>
       <c r="C144" t="n">
         <v>104.5199966430664</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>84.71593475341797</v>
+        <v>84.71595001220703</v>
       </c>
       <c r="C145" t="n">
         <v>106.9400024414062</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>92.10900115966797</v>
+        <v>92.10902404785156</v>
       </c>
       <c r="C146" t="n">
         <v>115.6699981689453</v>
@@ -4185,7 +4197,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>87.57004547119141</v>
+        <v>87.57005310058594</v>
       </c>
       <c r="C148" t="n">
         <v>109.9700012207031</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>87.06172180175781</v>
+        <v>87.06171417236328</v>
       </c>
       <c r="C149" t="n">
         <v>108.7799987792969</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>85.64509582519531</v>
+        <v>85.64510345458984</v>
       </c>
       <c r="C150" t="n">
         <v>107.0100021362305</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>83.39614105224609</v>
+        <v>83.39613342285156</v>
       </c>
       <c r="C151" t="n">
         <v>104.1999969482422</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>92.49980163574219</v>
+        <v>92.49981689453125</v>
       </c>
       <c r="C152" t="n">
         <v>114.9499969482422</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>92.20208740234375</v>
+        <v>92.20206451416016</v>
       </c>
       <c r="C153" t="n">
         <v>114.5800018310547</v>
@@ -4388,7 +4400,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>88.34230041503906</v>
+        <v>88.34230804443359</v>
       </c>
       <c r="C155" t="n">
         <v>109.0199966430664</v>
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>79.10451507568359</v>
+        <v>79.10453796386719</v>
       </c>
       <c r="C157" t="n">
         <v>97.62000274658203</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>84.55036926269531</v>
+        <v>84.55037689208984</v>
       </c>
       <c r="C158" t="n">
         <v>103.5</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>85.25289916992188</v>
+        <v>85.25290679931641</v>
       </c>
       <c r="C159" t="n">
         <v>104.3600006103516</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>82.69599151611328</v>
+        <v>82.69597625732422</v>
       </c>
       <c r="C160" t="n">
         <v>101.2300033569336</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>95.52805328369141</v>
+        <v>95.52804565429688</v>
       </c>
       <c r="C161" t="n">
         <v>116.0500030517578</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>87.22229766845703</v>
+        <v>87.22231292724609</v>
       </c>
       <c r="C162" t="n">
         <v>105.9599990844727</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>92.02958679199219</v>
+        <v>92.02957916259766</v>
       </c>
       <c r="C163" t="n">
         <v>111.8000030517578</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>96.16286468505859</v>
+        <v>96.16288757324219</v>
       </c>
       <c r="C164" t="n">
         <v>116</v>
@@ -4707,7 +4719,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>97.56388092041016</v>
+        <v>97.56388854980469</v>
       </c>
       <c r="C166" t="n">
         <v>117.6900024414062</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>104.3870468139648</v>
+        <v>104.3870391845703</v>
       </c>
       <c r="C167" t="n">
         <v>124.9199981689453</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>110.1027450561523</v>
+        <v>110.1027374267578</v>
       </c>
       <c r="C168" t="n">
         <v>131.7599945068359</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>116.4869689941406</v>
+        <v>116.4869842529297</v>
       </c>
       <c r="C169" t="n">
         <v>139.3999938964844</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>111.3142166137695</v>
+        <v>111.3142013549805</v>
       </c>
       <c r="C170" t="n">
         <v>132.3600006103516</v>
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>75.71483612060547</v>
+        <v>75.71485137939453</v>
       </c>
       <c r="C172" t="n">
         <v>90.02999877929688</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>81.37061309814453</v>
+        <v>81.37060546875</v>
       </c>
       <c r="C173" t="n">
         <v>95.76000213623047</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>82.68768310546875</v>
+        <v>82.68770599365234</v>
       </c>
       <c r="C174" t="n">
         <v>97.30999755859375</v>
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,7 +5038,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>85.96455383300781</v>
+        <v>85.96453857421875</v>
       </c>
       <c r="C177" t="n">
         <v>100.1900024414062</v>
@@ -5084,7 +5096,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>84.90039825439453</v>
+        <v>84.900390625</v>
       </c>
       <c r="C179" t="n">
         <v>98.04000091552734</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>102.0813522338867</v>
+        <v>102.0813674926758</v>
       </c>
       <c r="C180" t="n">
         <v>117.879997253418</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>110.0396957397461</v>
+        <v>110.0397033691406</v>
       </c>
       <c r="C181" t="n">
         <v>127.0699996948242</v>
@@ -5200,7 +5212,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>128.3636779785156</v>
+        <v>128.3636627197266</v>
       </c>
       <c r="C183" t="n">
         <v>147.1699981689453</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.7770538330078</v>
+        <v>132.7770385742188</v>
       </c>
       <c r="C184" t="n">
         <v>152.2299957275391</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>134.9453125</v>
+        <v>134.9453277587891</v>
       </c>
       <c r="C185" t="n">
         <v>153.8099975585938</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>144.0960693359375</v>
+        <v>144.0960388183594</v>
       </c>
       <c r="C186" t="n">
         <v>164.2400054931641</v>
@@ -5345,11 +5357,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>136.4631195068359</v>
+        <v>136.4630889892578</v>
       </c>
       <c r="C187" t="n">
         <v>155.5399932861328</v>
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>133.931640625</v>
+        <v>133.9316253662109</v>
       </c>
       <c r="C188" t="n">
         <v>151.7799987792969</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>141.1408996582031</v>
+        <v>141.1409301757812</v>
       </c>
       <c r="C189" t="n">
         <v>159.9499969482422</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>144.4411315917969</v>
+        <v>144.4410858154297</v>
       </c>
       <c r="C190" t="n">
         <v>163.6900024414062</v>
@@ -5461,7 +5473,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5519,7 +5531,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5548,11 +5560,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>132.7064361572266</v>
+        <v>132.7064666748047</v>
       </c>
       <c r="C194" t="n">
         <v>148.6000061035156</v>
@@ -5577,11 +5589,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>126.6337356567383</v>
+        <v>126.6337738037109</v>
       </c>
       <c r="C195" t="n">
         <v>141.8000030517578</v>
@@ -5606,7 +5618,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>107.3839416503906</v>
+        <v>107.3839569091797</v>
       </c>
       <c r="C197" t="n">
         <v>119.3600006103516</v>
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>118.9626388549805</v>
+        <v>118.9626159667969</v>
       </c>
       <c r="C198" t="n">
         <v>132.2299957275391</v>
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>101.3112106323242</v>
+        <v>101.3112258911133</v>
       </c>
       <c r="C199" t="n">
         <v>112.6100006103516</v>
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>104.7033157348633</v>
+        <v>104.7033386230469</v>
       </c>
       <c r="C200" t="n">
         <v>115.3600006103516</v>
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>103.2239303588867</v>
+        <v>103.2239227294922</v>
       </c>
       <c r="C201" t="n">
         <v>113.7300033569336</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>94.84654998779297</v>
+        <v>94.84654235839844</v>
       </c>
       <c r="C202" t="n">
         <v>104.5</v>
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>115.2737350463867</v>
+        <v>115.2737274169922</v>
       </c>
       <c r="C203" t="n">
         <v>125.879997253418</v>
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>126.537353515625</v>
+        <v>126.5373382568359</v>
       </c>
       <c r="C204" t="n">
         <v>138.1799926757812</v>
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>122.8011474609375</v>
+        <v>122.8011245727539</v>
       </c>
       <c r="C205" t="n">
         <v>134.1000061035156</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>129.1141052246094</v>
+        <v>129.1141204833984</v>
       </c>
       <c r="C206" t="n">
         <v>139.9600067138672</v>
@@ -5925,7 +5937,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>120.2119293212891</v>
+        <v>120.2119140625</v>
       </c>
       <c r="C208" t="n">
         <v>130.3099975585938</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>128.5282592773438</v>
+        <v>128.5282440185547</v>
       </c>
       <c r="C209" t="n">
         <v>138.2400054931641</v>
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>126.1759719848633</v>
+        <v>126.1759948730469</v>
       </c>
       <c r="C210" t="n">
         <v>135.7100067138672</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>135.2223968505859</v>
+        <v>135.2224426269531</v>
       </c>
       <c r="C211" t="n">
         <v>145.4400024414062</v>
@@ -6070,7 +6082,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>136.9842224121094</v>
+        <v>136.9842376708984</v>
       </c>
       <c r="C213" t="n">
         <v>146.3300018310547</v>
@@ -6128,11 +6140,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>135.7579193115234</v>
+        <v>135.7578887939453</v>
       </c>
       <c r="C214" t="n">
         <v>145.0200042724609</v>
@@ -6157,11 +6169,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>131.1391143798828</v>
+        <v>131.1390991210938</v>
       </c>
       <c r="C215" t="n">
         <v>139.0599975585938</v>
@@ -6186,11 +6198,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>147.1896362304688</v>
+        <v>147.1896667480469</v>
       </c>
       <c r="C216" t="n">
         <v>156.0800018310547</v>
@@ -6215,11 +6227,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>160.4110870361328</v>
+        <v>160.4110717773438</v>
       </c>
       <c r="C217" t="n">
         <v>170.1000061035156</v>
@@ -6244,11 +6256,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>165.4423217773438</v>
+        <v>165.4423370361328</v>
       </c>
       <c r="C218" t="n">
         <v>174.3600006103516</v>
@@ -6273,7 +6285,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6302,11 +6314,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>190.0556335449219</v>
+        <v>190.0556488037109</v>
       </c>
       <c r="C220" t="n">
         <v>200.3000030517578</v>
@@ -6331,7 +6343,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6360,11 +6372,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>193.3879699707031</v>
+        <v>193.3880157470703</v>
       </c>
       <c r="C222" t="n">
         <v>202.6300048828125</v>
@@ -6389,11 +6401,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>193.0348510742188</v>
+        <v>193.0348358154297</v>
       </c>
       <c r="C223" t="n">
         <v>202.2599945068359</v>
@@ -6418,7 +6430,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6447,11 +6459,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>215.7356414794922</v>
+        <v>215.7356262207031</v>
       </c>
       <c r="C225" t="n">
         <v>224.8000030517578</v>
@@ -6476,7 +6488,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6505,11 +6517,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>214.2768402099609</v>
+        <v>214.2768249511719</v>
       </c>
       <c r="C227" t="n">
         <v>221.9199981689453</v>
@@ -6534,11 +6546,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>241.119384765625</v>
+        <v>241.1194152832031</v>
       </c>
       <c r="C228" t="n">
         <v>249.7200012207031</v>
@@ -6563,11 +6575,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>231.4541473388672</v>
+        <v>231.4541625976562</v>
       </c>
       <c r="C229" t="n">
         <v>239.7100067138672</v>
@@ -6592,11 +6604,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>259.4269104003906</v>
+        <v>259.4268493652344</v>
       </c>
       <c r="C230" t="n">
         <v>267.2999877929688</v>
@@ -6621,11 +6633,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>256.8549499511719</v>
+        <v>256.8548889160156</v>
       </c>
       <c r="C231" t="n">
         <v>264.6499938964844</v>
@@ -6650,11 +6662,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>238.0748901367188</v>
+        <v>238.0748748779297</v>
       </c>
       <c r="C232" t="n">
         <v>245.3000030517578</v>
@@ -6679,7 +6691,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6708,7 +6720,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6737,11 +6749,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>283.1040649414062</v>
+        <v>283.10400390625</v>
       </c>
       <c r="C235" t="n">
         <v>289.9100036621094</v>
@@ -6766,7 +6778,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6795,7 +6807,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="C250" t="n">
-        <v>337.5299987792969</v>
+        <v>338.5599975585938</v>
       </c>
       <c r="D250" t="n">
-        <v>123897600</v>
+        <v>130831900</v>
       </c>
       <c r="E250" t="n">
         <v>23.35</v>
       </c>
       <c r="F250" t="n">
-        <v>14.45524620039815</v>
+        <v>14.49935749715605</v>
       </c>
       <c r="G250" t="n">
         <v>2658186195</v>
       </c>
       <c r="H250" t="n">
-        <v>897217583153.4938</v>
+        <v>899955511689.4875</v>
       </c>
       <c r="I250" t="n">
-        <v>0.04660982749554909</v>
+        <v>0.049218485990971</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I10" t="n">
         <v>3.96</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I11" t="n">
         <v>4.5</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I12" t="n">
         <v>4.68</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K12" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I13" t="n">
         <v>4.69</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K13" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I14" t="n">
         <v>4.48</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K14" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I15" t="n">
         <v>4.510000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="K15" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I16" t="n">
         <v>4.450000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="K16" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I17" t="n">
         <v>4.83</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="K17" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I18" t="n">
         <v>5.2</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K18" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I19" t="n">
         <v>5.48</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K19" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I20" t="n">
         <v>5.87</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K20" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I21" t="n">
         <v>4.300000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K21" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I22" t="n">
         <v>4.35</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K22" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I23" t="n">
         <v>4.039999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K23" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I24" t="n">
         <v>3.899999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K24" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I25" t="n">
         <v>5.43</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K25" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I26" t="n">
         <v>5.29</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K26" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I27" t="n">
         <v>5.459999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K27" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I28" t="n">
         <v>5.539999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="K28" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I29" t="n">
         <v>5.859999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K29" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I30" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="K30" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I31" t="n">
         <v>5.9</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K31" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I32" t="n">
         <v>5.91</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K32" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I33" t="n">
         <v>5.81</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K33" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I34" t="n">
         <v>6.19</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="K34" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I35" t="n">
         <v>6.49</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K35" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I36" t="n">
         <v>6.76</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K36" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I37" t="n">
         <v>6.94</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K37" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I38" t="n">
         <v>6.31</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K38" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I39" t="n">
         <v>7.03</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K39" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I40" t="n">
         <v>7.5</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K40" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I41" t="n">
         <v>8.08</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K41" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I42" t="n">
         <v>9</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K42" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I43" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K43" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I44" t="n">
         <v>9.809999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K44" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I45" t="n">
         <v>10.15</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K45" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I46" t="n">
         <v>10.72</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K46" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I47" t="n">
         <v>8.85</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K47" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I48" t="n">
         <v>7.41</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="K48" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I49" t="n">
         <v>7.65</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="K49" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I50" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K50" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I51" t="n">
         <v>12.6</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K51" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44410</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I52" t="n">
         <v>15</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44410</v>
       </c>
       <c r="K52" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I53" t="n">
         <v>15.82</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K53" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I54" t="n">
         <v>15.36</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I55" t="n">
         <v>13.49</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K55" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I56" t="n">
         <v>12.47</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K56" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I57" t="n">
         <v>11.85</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K57" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I58" t="n">
         <v>12.09</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K58" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I59" t="n">
         <v>13.56</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="K59" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I60" t="n">
         <v>15.55</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K60" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I61" t="n">
         <v>16.76</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K61" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I62" t="n">
         <v>16.23</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K62" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I63" t="n">
         <v>16.57</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K63" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I64" t="n">
         <v>17.94</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K64" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I65" t="n">
         <v>17.98</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K65" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I66" t="n">
         <v>19.75</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K66" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I67" t="n">
         <v>20.38</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K67" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I68" t="n">
         <v>19.5</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K68" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I69" t="n">
         <v>20.2</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K69" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I70" t="n">
         <v>20.02</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K70" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I71" t="n">
         <v>20.89</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K71" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I72" t="n">
         <v>23.35</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K72" t="n">
@@ -10549,52 +10561,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10623,10 +10635,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C3" t="n">
@@ -10655,10 +10667,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="C4" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="C5" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="C7" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C12" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="C13" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="C14" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="C15" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C18" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C19" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C20" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C21" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C22" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C23" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C24" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C25" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="C26" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C27" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="C28" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C29" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C31" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="C32" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C33" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C36" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C38" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C39" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C40" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C41" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C43" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="C44" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C45" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="C46" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="C47" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C48" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C49" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44410</v>
       </c>
       <c r="C50" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C51" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C52" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C53" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C54" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C55" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C56" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45049</v>
       </c>
       <c r="C57" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C59" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C60" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C62" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C63" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C64" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C66" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C67" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C68" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C70" t="n">
@@ -12817,12 +12829,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/JPM.xlsx
+++ b/salidas/empresas/JPM.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>23.46864891052246</v>
+        <v>23.46864128112793</v>
       </c>
       <c r="C2" t="n">
         <v>39.75</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>24.28931999206543</v>
+        <v>24.28930473327637</v>
       </c>
       <c r="C3" t="n">
         <v>41.13999938964844</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.58450698852539</v>
+        <v>24.58452415466309</v>
       </c>
       <c r="C4" t="n">
         <v>41.63999938964844</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>27.01167106628418</v>
+        <v>27.01167488098145</v>
       </c>
       <c r="C5" t="n">
         <v>45.38000106811523</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>25.38073348999023</v>
+        <v>25.38074111938477</v>
       </c>
       <c r="C6" t="n">
         <v>42.63999938964844</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>24.99977111816406</v>
+        <v>24.99977493286133</v>
       </c>
       <c r="C7" t="n">
         <v>42</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>27.37613868713379</v>
+        <v>27.37614059448242</v>
       </c>
       <c r="C8" t="n">
         <v>45.61999893188477</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>27.4001522064209</v>
+        <v>27.4001407623291</v>
       </c>
       <c r="C9" t="n">
         <v>45.65999984741211</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.18027305603027</v>
+        <v>28.18026161193848</v>
       </c>
       <c r="C10" t="n">
         <v>46.95999908447266</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>28.67246246337891</v>
+        <v>28.67247772216797</v>
       </c>
       <c r="C11" t="n">
         <v>47.43999862670898</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>27.97136688232422</v>
+        <v>27.97137260437012</v>
       </c>
       <c r="C12" t="n">
         <v>46.27999877929688</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>29.1922550201416</v>
+        <v>29.19223403930664</v>
       </c>
       <c r="C13" t="n">
         <v>48.29999923706055</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.0000171661377</v>
+        <v>31.00000953674316</v>
       </c>
       <c r="C14" t="n">
         <v>50.93000030517578</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.06265830993652</v>
+        <v>30.06265449523926</v>
       </c>
       <c r="C15" t="n">
         <v>49.38999938964844</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>29.44790077209473</v>
+        <v>29.44788551330566</v>
       </c>
       <c r="C16" t="n">
         <v>48.38000106811523</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>31.93727684020996</v>
+        <v>31.93725776672363</v>
       </c>
       <c r="C17" t="n">
         <v>52.09999847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>31.77178382873535</v>
+        <v>31.77176475524902</v>
       </c>
       <c r="C18" t="n">
         <v>51.83000183105469</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>29.69980430603027</v>
+        <v>29.69982528686523</v>
       </c>
       <c r="C19" t="n">
         <v>48.45000076293945</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>27.18831062316895</v>
+        <v>27.18831443786621</v>
       </c>
       <c r="C20" t="n">
         <v>44.0099983215332</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>27.50337791442871</v>
+        <v>27.50338554382324</v>
       </c>
       <c r="C21" t="n">
         <v>44.52000045776367</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.30649757385254</v>
+        <v>28.30649185180664</v>
       </c>
       <c r="C22" t="n">
         <v>45.81999969482422</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>29.27132415771484</v>
+        <v>29.27131652832031</v>
       </c>
       <c r="C23" t="n">
         <v>47</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>27.18495559692383</v>
+        <v>27.18495750427246</v>
       </c>
       <c r="C25" t="n">
         <v>43.65000152587891</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.77967643737793</v>
+        <v>29.77968406677246</v>
       </c>
       <c r="C26" t="n">
         <v>47.40000152587891</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>25.53890609741211</v>
+        <v>25.53891372680664</v>
       </c>
       <c r="C27" t="n">
         <v>40.65000152587891</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>26.98391532897949</v>
+        <v>26.98391342163086</v>
       </c>
       <c r="C28" t="n">
         <v>42.95000076293945</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>30.1807746887207</v>
+        <v>30.18077087402344</v>
       </c>
       <c r="C29" t="n">
         <v>47.65000152587891</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>27.23551750183105</v>
+        <v>27.23552894592285</v>
       </c>
       <c r="C30" t="n">
         <v>43</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>21.73142242431641</v>
+        <v>21.73142433166504</v>
       </c>
       <c r="C31" t="n">
         <v>34.31000137329102</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.02263259887695</v>
+        <v>26.02262878417969</v>
       </c>
       <c r="C32" t="n">
         <v>40.63000106811523</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>24.65199661254883</v>
+        <v>24.65200042724609</v>
       </c>
       <c r="C33" t="n">
         <v>38.4900016784668</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.91033172607422</v>
+        <v>29.91032600402832</v>
       </c>
       <c r="C34" t="n">
         <v>46.70000076293945</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>26.62356758117676</v>
+        <v>26.62357139587402</v>
       </c>
       <c r="C35" t="n">
         <v>41.25</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.43399047851562</v>
+        <v>20.43398857116699</v>
       </c>
       <c r="C36" t="n">
         <v>31.65999984741211</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.35009002685547</v>
+        <v>20.35009384155273</v>
       </c>
       <c r="C37" t="n">
         <v>31.53000068664551</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>17.36453628540039</v>
+        <v>17.36454010009766</v>
       </c>
       <c r="C40" t="n">
         <v>26.57999992370605</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.59704780578613</v>
+        <v>21.59705352783203</v>
       </c>
       <c r="C41" t="n">
         <v>33</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>24.14943695068359</v>
+        <v>24.14944076538086</v>
       </c>
       <c r="C42" t="n">
         <v>36.90000152587891</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>22.3234920501709</v>
+        <v>22.32350540161133</v>
       </c>
       <c r="C43" t="n">
         <v>34.11000061035156</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.33185577392578</v>
+        <v>25.33186340332031</v>
       </c>
       <c r="C44" t="n">
         <v>38.65000152587891</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.48442459106445</v>
+        <v>28.48441505432129</v>
       </c>
       <c r="C45" t="n">
         <v>43.45999908447266</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>28.72036743164062</v>
+        <v>28.72036933898926</v>
       </c>
       <c r="C46" t="n">
         <v>43.81999969482422</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.40988349914551</v>
+        <v>27.40989875793457</v>
       </c>
       <c r="C47" t="n">
         <v>41.77000045776367</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.34426307678223</v>
+        <v>27.34426498413086</v>
       </c>
       <c r="C49" t="n">
         <v>41.66999816894531</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.58352279663086</v>
+        <v>25.58351516723633</v>
       </c>
       <c r="C50" t="n">
         <v>38.93999862670898</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>27.5742130279541</v>
+        <v>27.57422256469727</v>
       </c>
       <c r="C51" t="n">
         <v>41.97000122070312</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>29.40067100524902</v>
+        <v>29.40067863464355</v>
       </c>
       <c r="C52" t="n">
         <v>44.75</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>28.00627899169922</v>
+        <v>28.00627708435059</v>
       </c>
       <c r="C53" t="n">
         <v>42.58000183105469</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>26.03309059143066</v>
+        <v>26.03307151794434</v>
       </c>
       <c r="C54" t="n">
         <v>39.58000183105469</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.07961082458496</v>
+        <v>24.07961845397949</v>
       </c>
       <c r="C55" t="n">
         <v>36.61000061035156</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>26.52972412109375</v>
+        <v>26.52972602844238</v>
       </c>
       <c r="C56" t="n">
         <v>40.27999877929688</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.9478931427002</v>
+        <v>23.94788360595703</v>
       </c>
       <c r="C57" t="n">
         <v>36.36000061035156</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.06755638122559</v>
+        <v>25.06756210327148</v>
       </c>
       <c r="C58" t="n">
         <v>38.06000137329102</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>24.81632232666016</v>
+        <v>24.81632804870605</v>
       </c>
       <c r="C59" t="n">
         <v>37.63000106811523</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>24.66464805603027</v>
+        <v>24.66464042663574</v>
       </c>
       <c r="C60" t="n">
         <v>37.40000152587891</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>27.97524833679199</v>
+        <v>27.97523307800293</v>
       </c>
       <c r="C61" t="n">
         <v>42.41999816894531</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>29.67116928100586</v>
+        <v>29.67118263244629</v>
       </c>
       <c r="C62" t="n">
         <v>44.93999862670898</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>30.82658958435059</v>
+        <v>30.82659721374512</v>
       </c>
       <c r="C63" t="n">
         <v>46.68999862670898</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>30.43705368041992</v>
+        <v>30.43705940246582</v>
       </c>
       <c r="C64" t="n">
         <v>46.09999847412109</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>30.29013061523438</v>
+        <v>30.29011535644531</v>
       </c>
       <c r="C65" t="n">
         <v>45.63000106811523</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>28.70360374450684</v>
+        <v>28.70358657836914</v>
       </c>
       <c r="C66" t="n">
         <v>43.2400016784668</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>27.17681121826172</v>
+        <v>27.17680549621582</v>
       </c>
       <c r="C67" t="n">
         <v>40.93999862670898</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>27.01650428771973</v>
+        <v>27.01650810241699</v>
       </c>
       <c r="C68" t="n">
         <v>40.45000076293945</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>25.08628845214844</v>
+        <v>25.08628273010254</v>
       </c>
       <c r="C69" t="n">
         <v>37.56000137329102</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>20.11711120605469</v>
+        <v>20.11711311340332</v>
       </c>
       <c r="C70" t="n">
         <v>30.1200008392334</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>20.86690902709961</v>
+        <v>20.86691665649414</v>
       </c>
       <c r="C72" t="n">
         <v>30.96999931335449</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>22.40312576293945</v>
+        <v>22.40313720703125</v>
       </c>
       <c r="C73" t="n">
         <v>33.25</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>25.31283950805664</v>
+        <v>25.31283569335938</v>
       </c>
       <c r="C74" t="n">
         <v>37.29999923706055</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>26.62937927246094</v>
+        <v>26.62938117980957</v>
       </c>
       <c r="C75" t="n">
         <v>39.2400016784668</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>31.20333290100098</v>
+        <v>31.20332717895508</v>
       </c>
       <c r="C76" t="n">
         <v>45.97999954223633</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>29.35837936401367</v>
+        <v>29.35837554931641</v>
       </c>
       <c r="C77" t="n">
         <v>42.97999954223633</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>22.6437931060791</v>
+        <v>22.64378929138184</v>
       </c>
       <c r="C78" t="n">
         <v>33.15000152587891</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.79557800292969</v>
+        <v>24.79557991027832</v>
       </c>
       <c r="C80" t="n">
         <v>36</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.58077812194824</v>
+        <v>25.58076667785645</v>
       </c>
       <c r="C81" t="n">
         <v>37.13999938964844</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>27.88124656677246</v>
+        <v>27.88125038146973</v>
       </c>
       <c r="C82" t="n">
         <v>40.47999954223633</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>28.91979217529297</v>
+        <v>28.91980361938477</v>
       </c>
       <c r="C83" t="n">
         <v>41.68000030517578</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>28.50349044799805</v>
+        <v>28.50347900390625</v>
       </c>
       <c r="C84" t="n">
         <v>41.08000183105469</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>30.50872802734375</v>
+        <v>30.50871849060059</v>
       </c>
       <c r="C85" t="n">
         <v>43.97000122070312</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>34.17646026611328</v>
+        <v>34.17647552490234</v>
       </c>
       <c r="C87" t="n">
         <v>48.91999816894531</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>38.3760871887207</v>
+        <v>38.37609100341797</v>
       </c>
       <c r="C90" t="n">
         <v>54.59000015258789</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>37.11071395874023</v>
+        <v>37.1107177734375</v>
       </c>
       <c r="C91" t="n">
         <v>52.79000091552734</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>39.46319580078125</v>
+        <v>39.46318817138672</v>
       </c>
       <c r="C92" t="n">
         <v>55.72999954223633</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>36.60239791870117</v>
+        <v>36.60240173339844</v>
       </c>
       <c r="C94" t="n">
         <v>51.68999862670898</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>36.76506805419922</v>
+        <v>36.76507568359375</v>
       </c>
       <c r="C95" t="n">
         <v>51.54000091552734</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>40.81680297851562</v>
+        <v>40.81679153442383</v>
       </c>
       <c r="C96" t="n">
         <v>57.22000122070312</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>39.7482795715332</v>
+        <v>39.74827575683594</v>
       </c>
       <c r="C98" t="n">
         <v>55.36000061035156</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>40.79655838012695</v>
+        <v>40.79656219482422</v>
       </c>
       <c r="C99" t="n">
         <v>56.81999969482422</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>43.58956527709961</v>
+        <v>43.58955764770508</v>
       </c>
       <c r="C100" t="n">
         <v>60.70999908447266</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>40.1505241394043</v>
+        <v>40.15053939819336</v>
       </c>
       <c r="C102" t="n">
         <v>55.56999969482422</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>41.63169860839844</v>
+        <v>41.63171005249023</v>
       </c>
       <c r="C103" t="n">
         <v>57.61999893188477</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>41.9591064453125</v>
+        <v>41.95912170410156</v>
       </c>
       <c r="C104" t="n">
         <v>57.66999816894531</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>43.25418090820312</v>
+        <v>43.25418853759766</v>
       </c>
       <c r="C105" t="n">
         <v>59.45000076293945</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>43.82897567749023</v>
+        <v>43.82898330688477</v>
       </c>
       <c r="C106" t="n">
         <v>60.2400016784668</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>44.06566619873047</v>
+        <v>44.0656623840332</v>
       </c>
       <c r="C108" t="n">
         <v>60.15999984741211</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>45.8382453918457</v>
+        <v>45.83826065063477</v>
       </c>
       <c r="C109" t="n">
         <v>62.58000183105469</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>40.08819961547852</v>
+        <v>40.08819198608398</v>
       </c>
       <c r="C110" t="n">
         <v>54.38000106811523</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>45.17480850219727</v>
+        <v>45.17479705810547</v>
       </c>
       <c r="C111" t="n">
         <v>61.27999877929688</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>44.65876007080078</v>
+        <v>44.65876770019531</v>
       </c>
       <c r="C112" t="n">
         <v>60.58000183105469</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>46.94438552856445</v>
+        <v>46.94438171386719</v>
       </c>
       <c r="C113" t="n">
         <v>63.2599983215332</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>48.8144416809082</v>
+        <v>48.81443405151367</v>
       </c>
       <c r="C114" t="n">
         <v>65.77999877929688</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>50.28377151489258</v>
+        <v>50.28376388549805</v>
       </c>
       <c r="C115" t="n">
         <v>67.76000213623047</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>51.18756103515625</v>
+        <v>51.18755722045898</v>
       </c>
       <c r="C116" t="n">
         <v>68.52999877929688</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>47.87863540649414</v>
+        <v>47.87864685058594</v>
       </c>
       <c r="C117" t="n">
         <v>64.09999847412109</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>48.33695220947266</v>
+        <v>48.33695983886719</v>
       </c>
       <c r="C119" t="n">
         <v>64.25</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>50.16511535644531</v>
+        <v>50.16510772705078</v>
       </c>
       <c r="C120" t="n">
         <v>66.68000030517578</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>49.67609786987305</v>
+        <v>49.67609024047852</v>
       </c>
       <c r="C121" t="n">
         <v>66.02999877929688</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>45.06368637084961</v>
+        <v>45.06369781494141</v>
       </c>
       <c r="C122" t="n">
         <v>59.5</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>44.85163497924805</v>
+        <v>44.85163879394531</v>
       </c>
       <c r="C124" t="n">
         <v>59.22000122070312</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>48.2203483581543</v>
+        <v>48.22035217285156</v>
       </c>
       <c r="C125" t="n">
         <v>63.20000076293945</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>49.79972076416016</v>
+        <v>49.79973220825195</v>
       </c>
       <c r="C126" t="n">
         <v>65.26999664306641</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>47.41159820556641</v>
+        <v>47.41159439086914</v>
       </c>
       <c r="C127" t="n">
         <v>62.13999938964844</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>49.18780136108398</v>
+        <v>49.18779373168945</v>
       </c>
       <c r="C128" t="n">
         <v>63.97000122070312</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>51.902099609375</v>
+        <v>51.90208435058594</v>
       </c>
       <c r="C129" t="n">
         <v>67.5</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>51.20237350463867</v>
+        <v>51.20236587524414</v>
       </c>
       <c r="C130" t="n">
         <v>66.58999633789062</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>53.64252471923828</v>
+        <v>53.64251708984375</v>
       </c>
       <c r="C131" t="n">
         <v>69.26000213623047</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>62.0924186706543</v>
+        <v>62.09241485595703</v>
       </c>
       <c r="C132" t="n">
         <v>80.16999816894531</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>66.83241271972656</v>
+        <v>66.83242797851562</v>
       </c>
       <c r="C133" t="n">
         <v>86.29000091552734</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>65.90941619873047</v>
+        <v>65.90940856933594</v>
       </c>
       <c r="C134" t="n">
         <v>84.62999725341797</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>70.57438659667969</v>
+        <v>70.57439422607422</v>
       </c>
       <c r="C135" t="n">
         <v>90.62000274658203</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>68.40934753417969</v>
+        <v>68.40933990478516</v>
       </c>
       <c r="C136" t="n">
         <v>87.83999633789062</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.14444732666016</v>
+        <v>68.14447784423828</v>
       </c>
       <c r="C137" t="n">
         <v>87</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>64.34558868408203</v>
+        <v>64.34560394287109</v>
       </c>
       <c r="C138" t="n">
         <v>82.15000152587891</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.59085083007812</v>
+        <v>71.59083557128906</v>
       </c>
       <c r="C139" t="n">
         <v>91.40000152587891</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>72.29969024658203</v>
+        <v>72.29966735839844</v>
       </c>
       <c r="C140" t="n">
         <v>91.80000305175781</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>71.58296203613281</v>
+        <v>71.58297729492188</v>
       </c>
       <c r="C141" t="n">
         <v>90.88999938964844</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>75.22156524658203</v>
+        <v>75.22158813476562</v>
       </c>
       <c r="C142" t="n">
         <v>95.51000213623047</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>79.70140075683594</v>
+        <v>79.70140838623047</v>
       </c>
       <c r="C143" t="n">
         <v>100.6100006103516</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>82.79883575439453</v>
+        <v>82.79881286621094</v>
       </c>
       <c r="C144" t="n">
         <v>104.5199966430664</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>84.71595001220703</v>
+        <v>84.71593475341797</v>
       </c>
       <c r="C145" t="n">
         <v>106.9400024414062</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>92.10902404785156</v>
+        <v>92.10901641845703</v>
       </c>
       <c r="C146" t="n">
         <v>115.6699981689453</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>91.9736328125</v>
+        <v>91.97364044189453</v>
       </c>
       <c r="C147" t="n">
         <v>115.5</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>85.64510345458984</v>
+        <v>85.64508819580078</v>
       </c>
       <c r="C150" t="n">
         <v>107.0100021362305</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>83.39613342285156</v>
+        <v>83.39611053466797</v>
       </c>
       <c r="C151" t="n">
         <v>104.1999969482422</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>92.49981689453125</v>
+        <v>92.49980926513672</v>
       </c>
       <c r="C152" t="n">
         <v>114.9499969482422</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>90.80189514160156</v>
+        <v>90.80190277099609</v>
       </c>
       <c r="C154" t="n">
         <v>112.8399963378906</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>88.34230804443359</v>
+        <v>88.34226989746094</v>
       </c>
       <c r="C155" t="n">
         <v>109.0199966430664</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>90.10071563720703</v>
+        <v>90.10070037841797</v>
       </c>
       <c r="C156" t="n">
         <v>111.1900024414062</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>79.10453796386719</v>
+        <v>79.10450744628906</v>
       </c>
       <c r="C157" t="n">
         <v>97.62000274658203</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>84.55037689208984</v>
+        <v>84.55036926269531</v>
       </c>
       <c r="C158" t="n">
         <v>103.5</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>85.25290679931641</v>
+        <v>85.25292205810547</v>
       </c>
       <c r="C159" t="n">
         <v>104.3600006103516</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>82.69597625732422</v>
+        <v>82.69598388671875</v>
       </c>
       <c r="C160" t="n">
         <v>101.2300033569336</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>92.02957916259766</v>
+        <v>92.02959442138672</v>
       </c>
       <c r="C163" t="n">
         <v>111.8000030517578</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>96.16288757324219</v>
+        <v>96.16287994384766</v>
       </c>
       <c r="C164" t="n">
         <v>116</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>91.07289123535156</v>
+        <v>91.07290649414062</v>
       </c>
       <c r="C165" t="n">
         <v>109.8600006103516</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>97.56388854980469</v>
+        <v>97.56387329101562</v>
       </c>
       <c r="C166" t="n">
         <v>117.6900024414062</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>104.3870391845703</v>
+        <v>104.3870468139648</v>
       </c>
       <c r="C167" t="n">
         <v>124.9199981689453</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>110.1027374267578</v>
+        <v>110.1027679443359</v>
       </c>
       <c r="C168" t="n">
         <v>131.7599945068359</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>111.3142013549805</v>
+        <v>111.314208984375</v>
       </c>
       <c r="C170" t="n">
         <v>132.3600006103516</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>75.71485137939453</v>
+        <v>75.71482849121094</v>
       </c>
       <c r="C172" t="n">
         <v>90.02999877929688</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>81.37060546875</v>
+        <v>81.37063598632812</v>
       </c>
       <c r="C173" t="n">
         <v>95.76000213623047</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>79.92605590820312</v>
+        <v>79.92606353759766</v>
       </c>
       <c r="C175" t="n">
         <v>94.05999755859375</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>82.9185791015625</v>
+        <v>82.91857147216797</v>
       </c>
       <c r="C176" t="n">
         <v>96.63999938964844</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>85.96453857421875</v>
+        <v>85.96454620361328</v>
       </c>
       <c r="C177" t="n">
         <v>100.1900024414062</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>82.60111236572266</v>
+        <v>82.60112762451172</v>
       </c>
       <c r="C178" t="n">
         <v>96.26999664306641</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>84.900390625</v>
+        <v>84.90038299560547</v>
       </c>
       <c r="C179" t="n">
         <v>98.04000091552734</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>102.0813674926758</v>
+        <v>102.0813751220703</v>
       </c>
       <c r="C180" t="n">
         <v>117.879997253418</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>112.2277069091797</v>
+        <v>112.2276992797852</v>
       </c>
       <c r="C182" t="n">
         <v>128.6699981689453</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>132.7770385742188</v>
+        <v>132.7770233154297</v>
       </c>
       <c r="C184" t="n">
         <v>152.2299957275391</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>134.9453277587891</v>
+        <v>134.9453125</v>
       </c>
       <c r="C185" t="n">
         <v>153.8099975585938</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>144.0960388183594</v>
+        <v>144.0960540771484</v>
       </c>
       <c r="C186" t="n">
         <v>164.2400054931641</v>
@@ -5361,7 +5361,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>136.4630889892578</v>
+        <v>136.4631195068359</v>
       </c>
       <c r="C187" t="n">
         <v>155.5399932861328</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>141.1409301757812</v>
+        <v>141.1408843994141</v>
       </c>
       <c r="C189" t="n">
         <v>159.9499969482422</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>144.4410858154297</v>
+        <v>144.4411010742188</v>
       </c>
       <c r="C190" t="n">
         <v>163.6900024414062</v>
@@ -5506,7 +5506,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>140.9971466064453</v>
+        <v>140.9971618652344</v>
       </c>
       <c r="C192" t="n">
         <v>158.8300018310547</v>
@@ -5593,7 +5593,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>126.6337738037109</v>
+        <v>126.6337661743164</v>
       </c>
       <c r="C195" t="n">
         <v>141.8000030517578</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>121.7398681640625</v>
+        <v>121.7398986816406</v>
       </c>
       <c r="C196" t="n">
         <v>136.3200073242188</v>
@@ -5651,7 +5651,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>107.3839569091797</v>
+        <v>107.3839492797852</v>
       </c>
       <c r="C197" t="n">
         <v>119.3600006103516</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>118.9626159667969</v>
+        <v>118.9626235961914</v>
       </c>
       <c r="C198" t="n">
         <v>132.2299957275391</v>
@@ -5709,7 +5709,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>101.3112258911133</v>
+        <v>101.3112182617188</v>
       </c>
       <c r="C199" t="n">
         <v>112.6100006103516</v>
@@ -5796,7 +5796,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>94.84654235839844</v>
+        <v>94.8465576171875</v>
       </c>
       <c r="C202" t="n">
         <v>104.5</v>
@@ -5854,7 +5854,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>126.5373382568359</v>
+        <v>126.5373611450195</v>
       </c>
       <c r="C204" t="n">
         <v>138.1799926757812</v>
@@ -5883,7 +5883,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>122.8011245727539</v>
+        <v>122.801139831543</v>
       </c>
       <c r="C205" t="n">
         <v>134.1000061035156</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>129.1141204833984</v>
+        <v>129.1141357421875</v>
       </c>
       <c r="C206" t="n">
         <v>139.9600067138672</v>
@@ -6057,7 +6057,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>135.2224426269531</v>
+        <v>135.222412109375</v>
       </c>
       <c r="C211" t="n">
         <v>145.4400024414062</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>147.8714599609375</v>
+        <v>147.8714447021484</v>
       </c>
       <c r="C212" t="n">
         <v>157.9600067138672</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>136.9842376708984</v>
+        <v>136.9842224121094</v>
       </c>
       <c r="C213" t="n">
         <v>146.3300018310547</v>
@@ -6144,7 +6144,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>135.7578887939453</v>
+        <v>135.7579040527344</v>
       </c>
       <c r="C214" t="n">
         <v>145.0200042724609</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>147.1896667480469</v>
+        <v>147.1896209716797</v>
       </c>
       <c r="C216" t="n">
         <v>156.0800018310547</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>165.4423370361328</v>
+        <v>165.4423217773438</v>
       </c>
       <c r="C218" t="n">
         <v>174.3600006103516</v>
@@ -6289,7 +6289,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>176.5439300537109</v>
+        <v>176.5439605712891</v>
       </c>
       <c r="C219" t="n">
         <v>186.0599975585938</v>
@@ -6376,7 +6376,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>193.3880157470703</v>
+        <v>193.3880004882812</v>
       </c>
       <c r="C222" t="n">
         <v>202.6300048828125</v>
@@ -6434,7 +6434,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>204.2194976806641</v>
+        <v>204.2195129394531</v>
       </c>
       <c r="C224" t="n">
         <v>212.8000030517578</v>
@@ -6521,7 +6521,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>214.2768249511719</v>
+        <v>214.2768402099609</v>
       </c>
       <c r="C227" t="n">
         <v>221.9199981689453</v>
@@ -6579,7 +6579,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>231.4541625976562</v>
+        <v>231.4541473388672</v>
       </c>
       <c r="C229" t="n">
         <v>239.7100067138672</v>
@@ -6608,7 +6608,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>259.4268493652344</v>
+        <v>259.4269104003906</v>
       </c>
       <c r="C230" t="n">
         <v>267.2999877929688</v>
@@ -6637,7 +6637,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>256.8548889160156</v>
+        <v>256.8549194335938</v>
       </c>
       <c r="C231" t="n">
         <v>264.6499938964844</v>
@@ -6666,7 +6666,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>238.0748748779297</v>
+        <v>238.0748901367188</v>
       </c>
       <c r="C232" t="n">
         <v>245.3000030517578</v>
@@ -6753,7 +6753,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>283.10400390625</v>
+        <v>283.1040649414062</v>
       </c>
       <c r="C235" t="n">
         <v>289.9100036621094</v>
@@ -6811,7 +6811,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>295.7618408203125</v>
+        <v>295.7618713378906</v>
       </c>
       <c r="C237" t="n">
         <v>301.4200134277344</v>
